--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-12).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-12).xlsx
@@ -938,31 +938,31 @@
     <t>215</t>
   </si>
   <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>R$ 9.015,48</t>
-  </si>
-  <si>
-    <t>97.7</t>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 8.990,35</t>
+  </si>
+  <si>
+    <t>97.4</t>
   </si>
   <si>
     <t>60.2</t>
   </si>
   <si>
-    <t>8.15</t>
-  </si>
-  <si>
-    <t>25.8</t>
-  </si>
-  <si>
-    <t>11.1</t>
+    <t>8.12</t>
+  </si>
+  <si>
+    <t>25.7</t>
+  </si>
+  <si>
+    <t>11.0</t>
   </si>
   <si>
     <t>6.2</t>
   </si>
   <si>
-    <t>27.0%</t>
+    <t>27.3%</t>
   </si>
   <si>
     <t>17.9%</t>
@@ -24782,7 +24782,7 @@
         <v>19847</v>
       </c>
       <c r="B156" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C156" s="4">
         <v>51</v>
@@ -24812,18 +24812,30 @@
         <v>58</v>
       </c>
       <c r="L156" s="4"/>
-      <c r="M156" s="5"/>
-      <c r="N156" s="6"/>
+      <c r="M156" s="5">
+        <v>6760.4700000000003</v>
+      </c>
+      <c r="N156" s="6">
+        <v>76</v>
+      </c>
       <c r="O156" s="6">
         <v>57</v>
       </c>
-      <c r="P156" s="7"/>
-      <c r="Q156" s="8"/>
-      <c r="R156" s="8"/>
+      <c r="P156" s="7">
+        <v>5.7046743902439028</v>
+      </c>
+      <c r="Q156" s="8">
+        <v>19.850000000000001</v>
+      </c>
+      <c r="R156" s="8">
+        <v>7.3523385964912285</v>
+      </c>
       <c r="S156" s="8">
         <v>7</v>
       </c>
-      <c r="T156" s="9"/>
+      <c r="T156" s="9">
+        <v>0.26315789473684209</v>
+      </c>
       <c r="U156" s="9">
         <v>0.035087719298245612</v>
       </c>
@@ -25125,7 +25137,7 @@
         <v>19863</v>
       </c>
       <c r="B159" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C159" s="4">
         <v>51</v>
@@ -25155,18 +25167,30 @@
         <v>58</v>
       </c>
       <c r="L159" s="4"/>
-      <c r="M159" s="5"/>
-      <c r="N159" s="6"/>
+      <c r="M159" s="5">
+        <v>6646.3599999999997</v>
+      </c>
+      <c r="N159" s="6">
+        <v>70</v>
+      </c>
       <c r="O159" s="6">
         <v>51</v>
       </c>
-      <c r="P159" s="7"/>
-      <c r="Q159" s="8"/>
-      <c r="R159" s="8"/>
+      <c r="P159" s="7">
+        <v>4.8057142857142852</v>
+      </c>
+      <c r="Q159" s="8">
+        <v>17.210456862745097</v>
+      </c>
+      <c r="R159" s="8">
+        <v>4.9892156862745098</v>
+      </c>
       <c r="S159" s="8">
         <v>7</v>
       </c>
-      <c r="T159" s="9"/>
+      <c r="T159" s="9">
+        <v>0.43137254901960786</v>
+      </c>
       <c r="U159" s="9">
         <v>0</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-12).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-12).xlsx
@@ -938,25 +938,25 @@
     <t>215</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 8.990,35</t>
-  </si>
-  <si>
-    <t>97.4</t>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 8.980,73</t>
+  </si>
+  <si>
+    <t>97.3</t>
   </si>
   <si>
     <t>60.2</t>
   </si>
   <si>
-    <t>8.12</t>
-  </si>
-  <si>
-    <t>25.7</t>
-  </si>
-  <si>
-    <t>11.0</t>
+    <t>8.14</t>
+  </si>
+  <si>
+    <t>26.1</t>
+  </si>
+  <si>
+    <t>11.4</t>
   </si>
   <si>
     <t>6.2</t>
@@ -16692,7 +16692,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -16722,14 +16722,26 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
+      <c r="M102" s="5">
+        <v>7209.7799999999997</v>
+      </c>
+      <c r="N102" s="6">
+        <v>74</v>
+      </c>
       <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
+      <c r="P102" s="7">
+        <v>13.509685135135134</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>99.531482222222223</v>
+      </c>
+      <c r="R102" s="8">
+        <v>80.575363043478262</v>
+      </c>
       <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
+      <c r="T102" s="9">
+        <v>0</v>
+      </c>
       <c r="U102" s="9"/>
       <c r="V102" s="9"/>
       <c r="W102" s="9"/>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-12).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-12).xlsx
@@ -938,22 +938,22 @@
     <t>215</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 8.980,73</t>
-  </si>
-  <si>
-    <t>97.3</t>
-  </si>
-  <si>
-    <t>60.2</t>
-  </si>
-  <si>
-    <t>8.14</t>
-  </si>
-  <si>
-    <t>26.1</t>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 8.985,69</t>
+  </si>
+  <si>
+    <t>97.2</t>
+  </si>
+  <si>
+    <t>60.1</t>
+  </si>
+  <si>
+    <t>8.13</t>
+  </si>
+  <si>
+    <t>26.2</t>
   </si>
   <si>
     <t>11.4</t>
@@ -965,7 +965,7 @@
     <t>27.3%</t>
   </si>
   <si>
-    <t>17.9%</t>
+    <t>18.0%</t>
   </si>
   <si>
     <t>1.0%</t>
@@ -977,7 +977,7 @@
     <t>2.8%</t>
   </si>
   <si>
-    <t>0.9%</t>
+    <t>0.8%</t>
   </si>
   <si>
     <t>0.3%</t>
@@ -989,22 +989,22 @@
     <t>2.2%</t>
   </si>
   <si>
-    <t>6.6%</t>
-  </si>
-  <si>
-    <t>2284.0</t>
-  </si>
-  <si>
-    <t>1991.0</t>
-  </si>
-  <si>
-    <t>115.0</t>
-  </si>
-  <si>
-    <t>48.0</t>
-  </si>
-  <si>
-    <t>316.0</t>
+    <t>6.7%</t>
+  </si>
+  <si>
+    <t>2302.0</t>
+  </si>
+  <si>
+    <t>2009.0</t>
+  </si>
+  <si>
+    <t>116.0</t>
+  </si>
+  <si>
+    <t>49.0</t>
+  </si>
+  <si>
+    <t>317.0</t>
   </si>
   <si>
     <t>95.0</t>
@@ -1016,13 +1016,10 @@
     <t>657.0</t>
   </si>
   <si>
-    <t>242.0</t>
-  </si>
-  <si>
-    <t>736.0</t>
-  </si>
-  <si>
-    <t>0.8%</t>
+    <t>246.0</t>
+  </si>
+  <si>
+    <t>748.0</t>
   </si>
   <si>
     <t>87.0</t>
@@ -14779,7 +14776,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14807,14 +14804,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>9904.25</v>
+      </c>
+      <c r="N89" s="6">
+        <v>88</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>6.3304032967032962</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>27.465580434782609</v>
+      </c>
+      <c r="R89" s="8">
+        <v>14.632935714285715</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.10869565217391304</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -16728,7 +16737,9 @@
       <c r="N102" s="6">
         <v>74</v>
       </c>
-      <c r="O102" s="6"/>
+      <c r="O102" s="6">
+        <v>47</v>
+      </c>
       <c r="P102" s="7">
         <v>13.509685135135134</v>
       </c>
@@ -16738,31 +16749,75 @@
       <c r="R102" s="8">
         <v>80.575363043478262</v>
       </c>
-      <c r="S102" s="8"/>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
       <c r="T102" s="9">
         <v>0</v>
       </c>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="U102" s="9">
+        <v>0.38297872340425532</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0.021276595744680851</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0.021276595743999999</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0.021276595744680851</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0.085106382978723402</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0.25531914893617019</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>18</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>18</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>4</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>12</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>
@@ -29107,7 +29162,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>51</v>
@@ -31761,7 +31816,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>51</v>
@@ -33394,7 +33449,7 @@
         <v>19980</v>
       </c>
       <c r="B216" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c t="s" r="C216" s="4">
         <v>51</v>
@@ -33633,10 +33688,10 @@
         <v>336</v>
       </c>
       <c t="s" r="AN217" s="11">
+        <v>322</v>
+      </c>
+      <c t="s" r="AO217" s="11">
         <v>337</v>
-      </c>
-      <c t="s" r="AO217" s="11">
-        <v>338</v>
       </c>
       <c r="AP217" s="12"/>
       <c t="s" r="AQ217" s="12">
@@ -33653,10 +33708,10 @@
         <v>59</v>
       </c>
       <c t="s" r="AX217" s="11">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c t="s" r="AY217" s="11">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AZ217" s="12"/>
       <c r="BA217" s="12"/>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-12).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-12).xlsx
@@ -938,37 +938,37 @@
     <t>215</t>
   </si>
   <si>
-    <t>28</t>
+    <t>22</t>
   </si>
   <si>
-    <t>R$ 8.985,69</t>
+    <t>R$ 8.893,02</t>
   </si>
   <si>
-    <t>97.2</t>
+    <t>96.3</t>
   </si>
   <si>
-    <t>60.1</t>
+    <t>60.3</t>
   </si>
   <si>
-    <t>8.13</t>
+    <t>8.16</t>
   </si>
   <si>
-    <t>26.2</t>
+    <t>26.0</t>
   </si>
   <si>
-    <t>11.4</t>
+    <t>11.3</t>
   </si>
   <si>
-    <t>6.2</t>
+    <t>6.4</t>
   </si>
   <si>
-    <t>27.3%</t>
+    <t>27.2%</t>
   </si>
   <si>
-    <t>18.0%</t>
+    <t>17.5%</t>
   </si>
   <si>
-    <t>1.0%</t>
+    <t>1.1%</t>
   </si>
   <si>
     <t>0.4%</t>
@@ -983,28 +983,28 @@
     <t>0.3%</t>
   </si>
   <si>
-    <t>5.9%</t>
+    <t>5.7%</t>
   </si>
   <si>
     <t>2.2%</t>
   </si>
   <si>
-    <t>6.7%</t>
+    <t>6.5%</t>
   </si>
   <si>
-    <t>2302.0</t>
+    <t>2323.0</t>
   </si>
   <si>
-    <t>2009.0</t>
+    <t>2030.0</t>
   </si>
   <si>
-    <t>116.0</t>
+    <t>122.0</t>
   </si>
   <si>
     <t>49.0</t>
   </si>
   <si>
-    <t>317.0</t>
+    <t>319.0</t>
   </si>
   <si>
     <t>95.0</t>
@@ -1013,16 +1013,16 @@
     <t>36.0</t>
   </si>
   <si>
-    <t>657.0</t>
+    <t>664.0</t>
   </si>
   <si>
-    <t>246.0</t>
+    <t>249.0</t>
   </si>
   <si>
-    <t>748.0</t>
+    <t>750.0</t>
   </si>
   <si>
-    <t>87.0</t>
+    <t>88.0</t>
   </si>
   <si>
     <t>1</t>
@@ -2209,7 +2209,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2239,35 +2239,93 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="6"/>
+      <c r="M6" s="5">
+        <v>13093.129999999999</v>
+      </c>
+      <c r="N6" s="6">
+        <v>143</v>
+      </c>
+      <c r="O6" s="6">
+        <v>117</v>
+      </c>
+      <c r="P6" s="7">
+        <v>21.028873239436621</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>32.749429914529912</v>
+      </c>
+      <c r="R6" s="8">
+        <v>3.7840452991452991</v>
+      </c>
+      <c r="S6" s="8">
+        <v>7</v>
+      </c>
+      <c r="T6" s="9">
+        <v>0.13675213675213677</v>
+      </c>
+      <c r="U6" s="9">
+        <v>0.034188034188034191</v>
+      </c>
+      <c r="V6" s="9">
+        <v>0</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0.0085470085470085479</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0.02564102564102564</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP6" s="4">
         <v>58</v>
       </c>
@@ -9132,7 +9190,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9162,14 +9220,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>1063.2</v>
+      </c>
+      <c r="N51" s="6">
+        <v>11</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>5.0791666666666666</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>21.119999999999997</v>
+      </c>
+      <c r="R51" s="8">
+        <v>28.25</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0.59999999999999998</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -10201,33 +10271,79 @@
       <c r="L58" s="4"/>
       <c r="M58" s="5"/>
       <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>86</v>
+      </c>
       <c r="P58" s="7"/>
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.11627906976744186</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0.069767441860465115</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0.011627906976744186</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0.023255813953488372</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>10</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>6</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0.011627906976744186</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -24124,7 +24240,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>51</v>
@@ -24154,35 +24270,93 @@
         <v>58</v>
       </c>
       <c r="L151" s="4"/>
-      <c r="M151" s="5"/>
-      <c r="N151" s="6"/>
-      <c r="O151" s="6"/>
-      <c r="P151" s="7"/>
-      <c r="Q151" s="8"/>
-      <c r="R151" s="8"/>
-      <c r="S151" s="8"/>
-      <c r="T151" s="9"/>
-      <c r="U151" s="9"/>
-      <c r="V151" s="9"/>
-      <c r="W151" s="9"/>
-      <c r="X151" s="9"/>
-      <c r="Y151" s="9"/>
-      <c r="Z151" s="9"/>
-      <c r="AA151" s="9"/>
-      <c r="AB151" s="9"/>
-      <c r="AC151" s="9"/>
-      <c r="AD151" s="6"/>
-      <c r="AE151" s="6"/>
-      <c r="AF151" s="6"/>
-      <c r="AG151" s="6"/>
-      <c r="AH151" s="6"/>
-      <c r="AI151" s="6"/>
-      <c r="AJ151" s="6"/>
-      <c r="AK151" s="6"/>
-      <c r="AL151" s="6"/>
-      <c r="AM151" s="6"/>
-      <c r="AN151" s="9"/>
-      <c r="AO151" s="6"/>
+      <c r="M151" s="5">
+        <v>5111.71</v>
+      </c>
+      <c r="N151" s="6">
+        <v>59</v>
+      </c>
+      <c r="O151" s="6">
+        <v>48</v>
+      </c>
+      <c r="P151" s="7">
+        <v>4.971311475409836</v>
+      </c>
+      <c r="Q151" s="8">
+        <v>14.46180625</v>
+      </c>
+      <c r="R151" s="8">
+        <v>2.9482645833333332</v>
+      </c>
+      <c r="S151" s="8">
+        <v>7</v>
+      </c>
+      <c r="T151" s="9">
+        <v>0.625</v>
+      </c>
+      <c r="U151" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="V151" s="9">
+        <v>0</v>
+      </c>
+      <c r="W151" s="9">
+        <v>0</v>
+      </c>
+      <c r="X151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="AB151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD151" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK151" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO151" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP151" s="4">
         <v>58</v>
       </c>
@@ -25006,7 +25180,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>51</v>
@@ -25036,35 +25210,93 @@
         <v>58</v>
       </c>
       <c r="L157" s="4"/>
-      <c r="M157" s="5"/>
-      <c r="N157" s="6"/>
-      <c r="O157" s="6"/>
-      <c r="P157" s="7"/>
-      <c r="Q157" s="8"/>
-      <c r="R157" s="8"/>
-      <c r="S157" s="8"/>
-      <c r="T157" s="9"/>
-      <c r="U157" s="9"/>
-      <c r="V157" s="9"/>
-      <c r="W157" s="9"/>
-      <c r="X157" s="9"/>
-      <c r="Y157" s="9"/>
-      <c r="Z157" s="9"/>
-      <c r="AA157" s="9"/>
-      <c r="AB157" s="9"/>
-      <c r="AC157" s="9"/>
-      <c r="AD157" s="6"/>
-      <c r="AE157" s="6"/>
-      <c r="AF157" s="6"/>
-      <c r="AG157" s="6"/>
-      <c r="AH157" s="6"/>
-      <c r="AI157" s="6"/>
-      <c r="AJ157" s="6"/>
-      <c r="AK157" s="6"/>
-      <c r="AL157" s="6"/>
-      <c r="AM157" s="6"/>
-      <c r="AN157" s="9"/>
-      <c r="AO157" s="6"/>
+      <c r="M157" s="5">
+        <v>5914.7600000000002</v>
+      </c>
+      <c r="N157" s="6">
+        <v>65</v>
+      </c>
+      <c r="O157" s="6">
+        <v>48</v>
+      </c>
+      <c r="P157" s="7">
+        <v>8.8478499999999993</v>
+      </c>
+      <c r="Q157" s="8">
+        <v>19.677777083333336</v>
+      </c>
+      <c r="R157" s="8">
+        <v>3.9541666666666671</v>
+      </c>
+      <c r="S157" s="8">
+        <v>7</v>
+      </c>
+      <c r="T157" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="U157" s="9">
+        <v>0</v>
+      </c>
+      <c r="V157" s="9">
+        <v>0</v>
+      </c>
+      <c r="W157" s="9">
+        <v>0</v>
+      </c>
+      <c r="X157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO157" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP157" s="4">
         <v>58</v>
       </c>
@@ -25105,7 +25337,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -25135,35 +25367,93 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
-      <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
-      <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
-      <c r="U158" s="9"/>
-      <c r="V158" s="9"/>
-      <c r="W158" s="9"/>
-      <c r="X158" s="9"/>
-      <c r="Y158" s="9"/>
-      <c r="Z158" s="9"/>
-      <c r="AA158" s="9"/>
-      <c r="AB158" s="9"/>
-      <c r="AC158" s="9"/>
-      <c r="AD158" s="6"/>
-      <c r="AE158" s="6"/>
-      <c r="AF158" s="6"/>
-      <c r="AG158" s="6"/>
-      <c r="AH158" s="6"/>
-      <c r="AI158" s="6"/>
-      <c r="AJ158" s="6"/>
-      <c r="AK158" s="6"/>
-      <c r="AL158" s="6"/>
-      <c r="AM158" s="6"/>
-      <c r="AN158" s="9"/>
-      <c r="AO158" s="6"/>
+      <c r="M158" s="5">
+        <v>4880.6999999999998</v>
+      </c>
+      <c r="N158" s="6">
+        <v>52</v>
+      </c>
+      <c r="O158" s="6">
+        <v>40</v>
+      </c>
+      <c r="P158" s="7">
+        <v>7.1993716981132083</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>20.503332499999999</v>
+      </c>
+      <c r="R158" s="8">
+        <v>6.4733324999999997</v>
+      </c>
+      <c r="S158" s="8">
+        <v>7</v>
+      </c>
+      <c r="T158" s="9">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="U158" s="9">
+        <v>0</v>
+      </c>
+      <c r="V158" s="9">
+        <v>0</v>
+      </c>
+      <c r="W158" s="9">
+        <v>0</v>
+      </c>
+      <c r="X158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO158" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP158" s="4">
         <v>58</v>
       </c>
@@ -26088,7 +26378,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>51</v>
@@ -26118,35 +26408,93 @@
         <v>58</v>
       </c>
       <c r="L165" s="4"/>
-      <c r="M165" s="5"/>
-      <c r="N165" s="6"/>
-      <c r="O165" s="6"/>
-      <c r="P165" s="7"/>
-      <c r="Q165" s="8"/>
-      <c r="R165" s="8"/>
-      <c r="S165" s="8"/>
-      <c r="T165" s="9"/>
-      <c r="U165" s="9"/>
-      <c r="V165" s="9"/>
-      <c r="W165" s="9"/>
-      <c r="X165" s="9"/>
-      <c r="Y165" s="9"/>
-      <c r="Z165" s="9"/>
-      <c r="AA165" s="9"/>
-      <c r="AB165" s="9"/>
-      <c r="AC165" s="9"/>
-      <c r="AD165" s="6"/>
-      <c r="AE165" s="6"/>
-      <c r="AF165" s="6"/>
-      <c r="AG165" s="6"/>
-      <c r="AH165" s="6"/>
-      <c r="AI165" s="6"/>
-      <c r="AJ165" s="6"/>
-      <c r="AK165" s="6"/>
-      <c r="AL165" s="6"/>
-      <c r="AM165" s="6"/>
-      <c r="AN165" s="9"/>
-      <c r="AO165" s="6"/>
+      <c r="M165" s="5">
+        <v>6057.9300000000003</v>
+      </c>
+      <c r="N165" s="6">
+        <v>70</v>
+      </c>
+      <c r="O165" s="6">
+        <v>46</v>
+      </c>
+      <c r="P165" s="7">
+        <v>5.9065217391304348</v>
+      </c>
+      <c r="Q165" s="8">
+        <v>16.930434782608696</v>
+      </c>
+      <c r="R165" s="8">
+        <v>4.5906512195121953</v>
+      </c>
+      <c r="S165" s="8">
+        <v>7</v>
+      </c>
+      <c r="T165" s="9">
+        <v>0.54347826086956519</v>
+      </c>
+      <c r="U165" s="9">
+        <v>0.10869565217391304</v>
+      </c>
+      <c r="V165" s="9">
+        <v>0</v>
+      </c>
+      <c r="W165" s="9">
+        <v>0</v>
+      </c>
+      <c r="X165" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y165" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="9">
+        <v>0.10869565217391304</v>
+      </c>
+      <c r="AB165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD165" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK165" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO165" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP165" s="4">
         <v>58</v>
       </c>
